--- a/data/seed/portfolio/L-2024-9972/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2024-9972/vypiska_2026-07_09.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I185"/>
+  <dimension ref="A1:I153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -558,40 +558,40 @@
           <t>100</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n">
-        <v>16705000</v>
-      </c>
-      <c r="D10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n">
+        <v>18270000</v>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Angren Sut Mahsulotlari MChJ</t>
+          <t>Kamalak Logistik MChJ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>280529819</t>
+          <t>311145569</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000231471188001</t>
+          <t>20208000814837533001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №3308</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №206/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>01.07.2026</t>
+          <t>02.07.2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -599,33 +599,33 @@
           <t>101</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n">
-        <v>23876000</v>
-      </c>
-      <c r="D11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n">
+        <v>85368000</v>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Xiva Polimer MChJ</t>
+          <t>Kamalak Logistik MChJ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>279310125</t>
+          <t>311145569</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000196619411001</t>
+          <t>20208000814837533001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №31/26 от 01.07.2026, НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №4313 от 02.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
@@ -640,40 +640,40 @@
           <t>102</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n">
-        <v>37835000</v>
-      </c>
+      <c r="C12" s="2" t="n">
+        <v>108539000</v>
+      </c>
+      <c r="D12" s="2" t="n"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Omad Un Mahsulotlari MChJ</t>
+          <t>Mehnat Agro Servis AJ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>216111455</t>
+          <t>252981962</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000988148375001</t>
+          <t>20208000147118816001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО С/Ф №6630 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+          <t>Оплата за транспортные услуги по договору №186/26</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>02.07.2026</t>
+          <t>03.07.2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -682,39 +682,39 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>63990000</v>
+        <v>226804000</v>
       </c>
       <c r="D13" s="2" t="n"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Angren Sut Mahsulotlari MChJ</t>
+          <t>Mehnat Agro Servis AJ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>280529819</t>
+          <t>252981962</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000231471188001</t>
+          <t>20208000147118816001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №37/26</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №40/26</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>03.07.2026</t>
+          <t>05.07.2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -722,40 +722,35 @@
           <t>104</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n">
-        <v>117888000</v>
-      </c>
+      <c r="C14" s="2" t="n">
+        <v>109900000</v>
+      </c>
+      <c r="D14" s="2" t="n"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Oqtosh Qurilish MChJ</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>234191595</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-9972)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000183809069001</t>
+          <t>16307000394306942417</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №268/26 от 03.07.2026</t>
+          <t>Kredit shartnomasi L-2024-9972 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>03.07.2026</t>
+          <t>06.07.2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -765,21 +760,21 @@
       </c>
       <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="n">
-        <v>114936000</v>
+        <v>93440000</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Oqtosh Qurilish MChJ</t>
+          <t>Kamalak Logistik MChJ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>234191595</t>
+          <t>311145569</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20208000183809069001</t>
+          <t>20208000814837533001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -789,14 +784,14 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №1070 за поставленный товар</t>
+          <t>Shartnoma №49/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>03.07.2026</t>
+          <t>06.07.2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -806,38 +801,38 @@
       </c>
       <c r="C16" s="2" t="n"/>
       <c r="D16" s="2" t="n">
-        <v>23287000</v>
+        <v>78423000</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Andijon Qurilish Materiallari MChJ</t>
+          <t>Kamalak Logistik MChJ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>259709555</t>
+          <t>311145569</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000755707627001</t>
+          <t>20208000814837533001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №5139 от 03.07.2026, в т.ч. НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №1405 06.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>03.07.2026</t>
+          <t>06.07.2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -847,38 +842,38 @@
       </c>
       <c r="C17" s="2" t="n"/>
       <c r="D17" s="2" t="n">
-        <v>22935000</v>
+        <v>44249000</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Omad Un Mahsulotlari MChJ</t>
+          <t>Lazzat Mato MChJ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>216111455</t>
+          <t>219159581</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20208000988148375001</t>
+          <t>20208000380906903001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №7097 за поставленный товар</t>
+          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №1831 ОТ 06.07.2026, В Т.Ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>05.07.2026</t>
+          <t>06.07.2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -886,28 +881,33 @@
           <t>108</t>
         </is>
       </c>
-      <c r="C18" s="2" t="n">
-        <v>109900000</v>
-      </c>
-      <c r="D18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n">
+        <v>30693000</v>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-9972)</t>
+          <t>Kamalak Logistik MChJ</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>311145569</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>16307000394306942417</t>
+          <t>20208000814837533001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-9972 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>Оплата за продукцию по договору №91/26, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -924,31 +924,31 @@
       </c>
       <c r="C19" s="2" t="n"/>
       <c r="D19" s="2" t="n">
-        <v>88674000</v>
+        <v>25052000</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Omad Un Mahsulotlari MChJ</t>
+          <t>Kamalak Logistik MChJ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>216111455</t>
+          <t>311145569</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000988148375001</t>
+          <t>20208000814837533001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3076</t>
+          <t>Оплата за товар по счет-фактуре №7029 от 06.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
@@ -963,33 +963,33 @@
           <t>110</t>
         </is>
       </c>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="n">
-        <v>79017000</v>
-      </c>
+      <c r="C20" s="2" t="n">
+        <v>33127000</v>
+      </c>
+      <c r="D20" s="2" t="n"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Omad Un Mahsulotlari MChJ</t>
+          <t>Termiz Qurilish MChJ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>216111455</t>
+          <t>394974967</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20208000988148375001</t>
+          <t>20208000335850400001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №7170 за поставленный товар</t>
+          <t>Оплата за транспортные услуги по договору №54/26</t>
         </is>
       </c>
     </row>
@@ -1004,33 +1004,33 @@
           <t>111</t>
         </is>
       </c>
-      <c r="C21" s="2" t="n"/>
-      <c r="D21" s="2" t="n">
-        <v>73584000</v>
-      </c>
+      <c r="C21" s="2" t="n">
+        <v>57449000</v>
+      </c>
+      <c r="D21" s="2" t="n"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Andijon Qurilish Materiallari MChJ</t>
+          <t>Termiz Qurilish MChJ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>259709555</t>
+          <t>394974967</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000755707627001</t>
+          <t>20208000335850400001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №702 за поставленный товар</t>
+          <t>Оплата за сырье по договору №278/26 от 06.07.2026, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -1045,23 +1045,18 @@
           <t>112</t>
         </is>
       </c>
-      <c r="C22" s="2" t="n"/>
-      <c r="D22" s="2" t="n">
-        <v>61005000</v>
-      </c>
+      <c r="C22" s="2" t="n">
+        <v>105903000</v>
+      </c>
+      <c r="D22" s="2" t="n"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Andijon Qurilish Materiallari MChJ</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>259709555</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000755707627001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1071,7 +1066,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №122/26, НДС 12%</t>
+          <t>Заработная плата за июнь 2026 г. (перечисление на пластиковые карты)</t>
         </is>
       </c>
     </row>
@@ -1086,40 +1081,40 @@
           <t>113</t>
         </is>
       </c>
-      <c r="C23" s="2" t="n"/>
-      <c r="D23" s="2" t="n">
-        <v>31641000</v>
-      </c>
+      <c r="C23" s="2" t="n">
+        <v>117695000</v>
+      </c>
+      <c r="D23" s="2" t="n"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Namangan Sut MChJ</t>
+          <t>Termiz Qurilish MChJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>248247433</t>
+          <t>394974967</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000050167487001</t>
+          <t>20208000335850400001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №233/26 от 06.07.2026</t>
+          <t>Оплата за упаковочные материалы, с/ф №7588</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>07.07.2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1128,34 +1123,39 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>105903000</v>
+        <v>14425000</v>
       </c>
       <c r="D24" s="2" t="n"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Urganch Qurilish Materiallari AJ</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>257886564</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000155605963001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Заработная плата за июнь 2026 г. (перечисление на пластиковые карты)</t>
+          <t>Bino ijarasi uchun to'lov iyul</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07.07.2026</t>
+          <t>08.07.2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1165,21 +1165,21 @@
       </c>
       <c r="C25" s="2" t="n"/>
       <c r="D25" s="2" t="n">
-        <v>25263000</v>
+        <v>44785000</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Omad Un Mahsulotlari MChJ</t>
+          <t>Samarqand Savdo MChJ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>216111455</t>
+          <t>324743320</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000988148375001</t>
+          <t>20208000016748722001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1189,14 +1189,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №216/26 от 07.07.2026</t>
+          <t>Оплата за продукцию по договору №241/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07.07.2026</t>
+          <t>08.07.2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1205,39 +1205,39 @@
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>14425000</v>
+        <v>93580000</v>
       </c>
       <c r="D26" s="2" t="n"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Buxoro Qurilish MChJ</t>
+          <t>Mehnat Agro Servis AJ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>275672982</t>
+          <t>252981962</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000548740249001</t>
+          <t>20208000147118816001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Арендная плата за июль 2026 г. по договору №28/25</t>
+          <t>Оплата за товары согласно счет-фактуре №6408</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08.07.2026</t>
+          <t>09.07.2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1245,40 +1245,40 @@
           <t>117</t>
         </is>
       </c>
-      <c r="C27" s="2" t="n">
-        <v>18563000</v>
-      </c>
-      <c r="D27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="n">
+        <v>62810000</v>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sharq Un Mahsulotlari XK</t>
+          <t>Lazzat Mato MChJ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>227213724</t>
+          <t>219159581</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000657957353001</t>
+          <t>20208000380906903001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №85/26, QQS bilan</t>
+          <t>Оплата по счет-фактуре №2016 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08.07.2026</t>
+          <t>09.07.2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1286,40 +1286,40 @@
           <t>118</t>
         </is>
       </c>
-      <c r="C28" s="2" t="n">
-        <v>51934000</v>
-      </c>
-      <c r="D28" s="2" t="n"/>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n">
+        <v>45738000</v>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sarbon Logistik MChJ</t>
+          <t>Lazzat Mato MChJ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>399038768</t>
+          <t>219159581</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000109731235001</t>
+          <t>20208000380906903001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №20/26 от 08.07.2026, НДС 12%</t>
+          <t>Оплата по счет-фактуре №8468 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08.07.2026</t>
+          <t>10.07.2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1327,33 +1327,33 @@
           <t>119</t>
         </is>
       </c>
-      <c r="C29" s="2" t="n">
-        <v>53100000</v>
-      </c>
-      <c r="D29" s="2" t="n"/>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n">
+        <v>171063000</v>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Angren Sut Mahsulotlari MChJ</t>
+          <t>Jizzax Logistik MChJ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>280529819</t>
+          <t>295117016</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000231471188001</t>
+          <t>20208000270881567001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №8141</t>
+          <t>Shartnoma №268/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
@@ -1370,38 +1370,38 @@
       </c>
       <c r="C30" s="2" t="n"/>
       <c r="D30" s="2" t="n">
-        <v>20025000</v>
+        <v>21573000</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Omad Un Mahsulotlari MChJ</t>
+          <t>Lazzat Mato MChJ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>216111455</t>
+          <t>219159581</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20208000988148375001</t>
+          <t>20208000380906903001</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №31/26, QQS 12%</t>
+          <t>Оплата за товар по с/ф №1271 от 10.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1411,31 +1411,31 @@
       </c>
       <c r="C31" s="2" t="n"/>
       <c r="D31" s="2" t="n">
-        <v>15790000</v>
+        <v>404803000</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Yulduz Tikuv AJ</t>
+          <t>Kamalak Logistik MChJ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>263502137</t>
+          <t>311145569</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000123163885001</t>
+          <t>20208000814837533001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №208/26, НДС 12%</t>
+          <t>Оплата за продукцию по договору №46/26, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -1450,33 +1450,33 @@
           <t>122</t>
         </is>
       </c>
-      <c r="C32" s="2" t="n">
-        <v>166884000</v>
-      </c>
-      <c r="D32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="n">
+        <v>53793000</v>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Angren Sut Mahsulotlari MChJ</t>
+          <t>Kamalak Logistik MChJ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>280529819</t>
+          <t>311145569</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000231471188001</t>
+          <t>20208000814837533001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №6096</t>
+          <t>Оплата за продукцию по договору №207/26, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -1492,39 +1492,39 @@
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>297961000</v>
+        <v>32697000</v>
       </c>
       <c r="D33" s="2" t="n"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Xiva Polimer MChJ</t>
+          <t>Termiz Qurilish MChJ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>279310125</t>
+          <t>394974967</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000196619411001</t>
+          <t>20208000335850400001</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Оплата за траспортные услуги по дог. №27/26</t>
+          <t>Transport xizmatlari uchun to'lov, shartn. №216/26</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>14.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1534,38 +1534,38 @@
       </c>
       <c r="C34" s="2" t="n"/>
       <c r="D34" s="2" t="n">
-        <v>149541000</v>
+        <v>38626000</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Oqtosh Qurilish MChJ</t>
+          <t>Kattaqo'rg'on Logistik XK</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>234191595</t>
+          <t>250213761</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20208000183809069001</t>
+          <t>20208000316388526001</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №291/26 от 14.07.2026</t>
+          <t>Предоплата за товар по договору №202/26 от 15.07.2026</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>14.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1574,39 +1574,39 @@
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>14441000</v>
+        <v>36269000</v>
       </c>
       <c r="D35" s="2" t="n"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Termiz Qurilish MChJ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>394974967</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000335850400001</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Социальный налог за июнь 2026 г.</t>
+          <t>Оплата за транспортные услуги по дог. №153/26</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>14.07.2026</t>
+          <t>16.07.2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1640,14 +1640,14 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>JShDS iyun oyi uchun</t>
+          <t>Уплата социального налога за июнь</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>14.07.2026</t>
+          <t>16.07.2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1656,39 +1656,39 @@
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>63653000</v>
+        <v>14441000</v>
       </c>
       <c r="D37" s="2" t="n"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Angren Sut Mahsulotlari MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>280529819</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20208000231471188001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №269/26</t>
+          <t>Налог на доходы физических лиц за июнь 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>15.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1698,21 +1698,21 @@
       </c>
       <c r="C38" s="2" t="n"/>
       <c r="D38" s="2" t="n">
-        <v>100072000</v>
+        <v>40051000</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Omad Un Mahsulotlari MChJ</t>
+          <t>Samarqand Savdo MChJ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>216111455</t>
+          <t>324743320</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20208000988148375001</t>
+          <t>20208000016748722001</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1722,14 +1722,14 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №23/26 от 15.07.2026</t>
+          <t>Оплата за продукцию по договору №31/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>15.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1739,38 +1739,38 @@
       </c>
       <c r="C39" s="2" t="n"/>
       <c r="D39" s="2" t="n">
-        <v>91452000</v>
+        <v>34525000</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Omad Un Mahsulotlari MChJ</t>
+          <t>Kattaqo'rg'on Logistik XK</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>216111455</t>
+          <t>250213761</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20208000988148375001</t>
+          <t>20208000316388526001</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №5729 15.07.2026, QQS bilan</t>
+          <t>Оплата за продукцию по договору №163/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>15.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1779,39 +1779,39 @@
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>87044000</v>
+        <v>21818000</v>
       </c>
       <c r="D40" s="2" t="n"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ilhom Avto Ehtiyot MChJ</t>
+          <t>Termiz Qurilish MChJ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>240223444</t>
+          <t>394974967</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20208000946555911001</t>
+          <t>20208000335850400001</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №22/26</t>
+          <t>Оплата за сырье по договору №231/26 от 20.07.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1819,40 +1819,40 @@
           <t>131</t>
         </is>
       </c>
-      <c r="C41" s="2" t="n"/>
-      <c r="D41" s="2" t="n">
-        <v>40460000</v>
-      </c>
+      <c r="C41" s="2" t="n">
+        <v>186306000</v>
+      </c>
+      <c r="D41" s="2" t="n"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Yulduz Tikuv AJ</t>
+          <t>Mehnat Agro Servis AJ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>263502137</t>
+          <t>252981962</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20208000123163885001</t>
+          <t>20208000147118816001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №71/26 от 16.07.2026</t>
+          <t>Tovarlar uchun to'lov h/f №6941</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>21.07.2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1861,39 +1861,39 @@
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>25284000</v>
+        <v>23768000</v>
       </c>
       <c r="D42" s="2" t="n"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sarbon Logistik MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>399038768</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000109731235001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №66/26</t>
+          <t>Уплата налога на добавленную стоимость за июнь</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>21.07.2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1902,39 +1902,39 @@
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>28259000</v>
+        <v>172546000</v>
       </c>
       <c r="D43" s="2" t="n"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Qarshi Yog'och XK</t>
+          <t>Termiz Qurilish MChJ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>335788656</t>
+          <t>394974967</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000915560596001</t>
+          <t>20208000335850400001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-факуре №1025</t>
+          <t>ОПЛАТА ЗА УПАКОВОЧНЫЕ МАТЕРИАЛЫ, С/Ф №8511</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>22.07.2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1944,38 +1944,38 @@
       </c>
       <c r="C44" s="2" t="n"/>
       <c r="D44" s="2" t="n">
-        <v>85620000</v>
+        <v>125458000</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Omad Un Mahsulotlari MChJ</t>
+          <t>Lazzat Mato MChJ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>216111455</t>
+          <t>219159581</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000988148375001</t>
+          <t>20208000380906903001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №230/26, НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №4177</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>23.07.2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1985,38 +1985,38 @@
       </c>
       <c r="C45" s="2" t="n"/>
       <c r="D45" s="2" t="n">
-        <v>49497000</v>
+        <v>113335000</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Omad Un Mahsulotlari MChJ</t>
+          <t>Lazzat Mato MChJ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>216111455</t>
+          <t>219159581</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000988148375001</t>
+          <t>20208000380906903001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №1081 от 17.07.2026, в т.ч. НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartn. №18/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>23.07.2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2026,38 +2026,38 @@
       </c>
       <c r="C46" s="2" t="n"/>
       <c r="D46" s="2" t="n">
-        <v>83646000</v>
+        <v>36136000</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Omad Un Mahsulotlari MChJ</t>
+          <t>Kamalak Logistik MChJ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>216111455</t>
+          <t>311145569</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20208000988148375001</t>
+          <t>20208000814837533001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №2799 за поставленный товар</t>
+          <t>Оплата за продукцию по договору №256/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>23.07.2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2065,40 +2065,40 @@
           <t>137</t>
         </is>
       </c>
-      <c r="C47" s="2" t="n">
-        <v>24743000</v>
-      </c>
-      <c r="D47" s="2" t="n"/>
+      <c r="C47" s="2" t="n"/>
+      <c r="D47" s="2" t="n">
+        <v>18917000</v>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sarbon Logistik MChJ</t>
+          <t>Jizzax Logistik MChJ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>399038768</t>
+          <t>295117016</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000109731235001</t>
+          <t>20208000270881567001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №232/26</t>
+          <t>Оплата за товар по с/ф №3971 от 23.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>24.07.2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2106,40 +2106,40 @@
           <t>138</t>
         </is>
       </c>
-      <c r="C48" s="2" t="n">
-        <v>51397000</v>
-      </c>
-      <c r="D48" s="2" t="n"/>
+      <c r="C48" s="2" t="n"/>
+      <c r="D48" s="2" t="n">
+        <v>45515000</v>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Angren Sut Mahsulotlari MChJ</t>
+          <t>Kamalak Logistik MChJ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>280529819</t>
+          <t>311145569</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20208000231471188001</t>
+          <t>20208000814837533001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №216/26</t>
+          <t>Оплата по счет-фактуре №3170 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>24.07.2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2148,39 +2148,39 @@
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>498448000</v>
+        <v>31721000</v>
       </c>
       <c r="D49" s="2" t="n"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ilhom Avto Ehtiyot MChJ</t>
+          <t>Afrosiyob Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>240223444</t>
+          <t>354981983</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000946555911001</t>
+          <t>20208000002477817001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №31/26 от 20.07.2026, НДС 12%</t>
+          <t>Предоплата за материалы п договору №117/26</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>21.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2189,39 +2189,39 @@
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>40719000</v>
+        <v>9015000</v>
       </c>
       <c r="D50" s="2" t="n"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Xiva Polimer MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>279310125</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000196619411001</t>
+          <t>20208000501793101001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №5101</t>
+          <t>Elektr energiyasi uchun to'lov iyul</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>22.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2229,23 +2229,23 @@
           <t>141</t>
         </is>
       </c>
-      <c r="C51" s="2" t="n"/>
-      <c r="D51" s="2" t="n">
-        <v>99050000</v>
-      </c>
+      <c r="C51" s="2" t="n">
+        <v>28636000</v>
+      </c>
+      <c r="D51" s="2" t="n"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Oqtosh Qurilish MChJ</t>
+          <t>Termiz Qurilish MChJ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>234191595</t>
+          <t>394974967</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000183809069001</t>
+          <t>20208000335850400001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2255,14 +2255,14 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-актуре №7640 от 22.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №4582</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>22.07.2026</t>
+          <t>28.07.2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2272,38 +2272,38 @@
       </c>
       <c r="C52" s="2" t="n"/>
       <c r="D52" s="2" t="n">
-        <v>69680000</v>
+        <v>105967000</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Yulduz Tikuv AJ</t>
+          <t>Lazzat Mato MChJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>263502137</t>
+          <t>219159581</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000123163885001</t>
+          <t>20208000380906903001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №4779 за поставленный товар</t>
+          <t>Оплата за товар по счет-фактуре №1067 от 28.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>22.07.2026</t>
+          <t>29.07.2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2311,40 +2311,40 @@
           <t>143</t>
         </is>
       </c>
-      <c r="C53" s="2" t="n">
-        <v>23786000</v>
-      </c>
-      <c r="D53" s="2" t="n"/>
+      <c r="C53" s="2" t="n"/>
+      <c r="D53" s="2" t="n">
+        <v>49095000</v>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Samarqand Savdo MChJ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>324743320</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000016748722001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>НДС за июнь 2026 г.</t>
+          <t>Предоплата за товар по дог. №260/26 от 29.07.2026</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>23.07.2026</t>
+          <t>30.07.2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2354,38 +2354,38 @@
       </c>
       <c r="C54" s="2" t="n"/>
       <c r="D54" s="2" t="n">
-        <v>68361000</v>
+        <v>152164000</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Yulduz Tikuv AJ</t>
+          <t>Kamalak Logistik MChJ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>263502137</t>
+          <t>311145569</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000123163885001</t>
+          <t>20208000814837533001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №21/26, QQS 12%</t>
+          <t>Предоплата за товар по договору №53/26 от 30.07.2026</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>23.07.2026</t>
+          <t>30.07.2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2393,23 +2393,23 @@
           <t>145</t>
         </is>
       </c>
-      <c r="C55" s="2" t="n"/>
-      <c r="D55" s="2" t="n">
-        <v>28178000</v>
-      </c>
+      <c r="C55" s="2" t="n">
+        <v>82407000</v>
+      </c>
+      <c r="D55" s="2" t="n"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Oqtosh Qurilish MChJ</t>
+          <t>Termiz Qurilish MChJ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>234191595</t>
+          <t>394974967</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000183809069001</t>
+          <t>20208000335850400001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2419,14 +2419,14 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №86/26 от 23.07.2026</t>
+          <t>Оплата за транспортные услуги по договору №213/26</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>23.07.2026</t>
+          <t>30.07.2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2435,39 +2435,39 @@
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>28250000</v>
+        <v>486894000</v>
       </c>
       <c r="D56" s="2" t="n"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Qarshi Yog'och XK</t>
+          <t>Termiz Qurilish MChJ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>335788656</t>
+          <t>394974967</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000915560596001</t>
+          <t>20208000335850400001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТРАНСПОРТНЫЕ УСЛУГИ ПО ДОГ. №284/26</t>
+          <t>Оплата за транспортные услуги по дог. №108/26</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>24.07.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2477,21 +2477,21 @@
       </c>
       <c r="C57" s="2" t="n"/>
       <c r="D57" s="2" t="n">
-        <v>74966000</v>
+        <v>40833000</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Oqtosh Qurilish MChJ</t>
+          <t>Kamalak Logistik MChJ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>234191595</t>
+          <t>311145569</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000183809069001</t>
+          <t>20208000814837533001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2501,14 +2501,14 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №553 за поставленный товар</t>
+          <t>Оплата по счет-фактуре №3708 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>24.07.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2516,23 +2516,18 @@
           <t>148</t>
         </is>
       </c>
-      <c r="C58" s="2" t="n"/>
-      <c r="D58" s="2" t="n">
-        <v>18979000</v>
-      </c>
+      <c r="C58" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D58" s="2" t="n"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Jizzax Tikuv XK</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>234951170</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000692708815001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2542,14 +2537,14 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №6440 от 24.07.2026, в т.ч. НДС 12%</t>
+          <t>Плата за SMS-информирование</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>24.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2557,40 +2552,40 @@
           <t>149</t>
         </is>
       </c>
-      <c r="C59" s="2" t="n">
-        <v>9015000</v>
-      </c>
-      <c r="D59" s="2" t="n"/>
+      <c r="C59" s="2" t="n"/>
+      <c r="D59" s="2" t="n">
+        <v>1066656000</v>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Samarqand Savdo MChJ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>324743320</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000489915123001</t>
+          <t>20208000016748722001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию за июль 2026 г.</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2632</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>24.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2598,40 +2593,40 @@
           <t>150</t>
         </is>
       </c>
-      <c r="C60" s="2" t="n">
-        <v>35895000</v>
-      </c>
-      <c r="D60" s="2" t="n"/>
+      <c r="C60" s="2" t="n"/>
+      <c r="D60" s="2" t="n">
+        <v>10530000</v>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Angren Sut Mahsulotlari MChJ</t>
+          <t>Kamalak Logistik MChJ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>280529819</t>
+          <t>311145569</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000231471188001</t>
+          <t>20208000814837533001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №4988</t>
+          <t>Tovar uchun to'lov, hisob-faktura №2596 03.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2639,23 +2634,23 @@
           <t>151</t>
         </is>
       </c>
-      <c r="C61" s="2" t="n"/>
-      <c r="D61" s="2" t="n">
-        <v>121917000</v>
-      </c>
+      <c r="C61" s="2" t="n">
+        <v>12055000</v>
+      </c>
+      <c r="D61" s="2" t="n"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Andijon Qurilish Materiallari MChJ</t>
+          <t>Afrosiyob Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>259709555</t>
+          <t>354981983</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000755707627001</t>
+          <t>20208000002477817001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2665,14 +2660,14 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №285/26, НДС 12%</t>
+          <t>Оплата за транспортные услуги по договору №106/26</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2680,40 +2675,40 @@
           <t>152</t>
         </is>
       </c>
-      <c r="C62" s="2" t="n"/>
-      <c r="D62" s="2" t="n">
-        <v>79934000</v>
-      </c>
+      <c r="C62" s="2" t="n">
+        <v>38670000</v>
+      </c>
+      <c r="D62" s="2" t="n"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Ip-Kalava MChJ</t>
+          <t>Afrosiyob Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>328549819</t>
+          <t>354981983</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000310024778001</t>
+          <t>20208000002477817001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №5030 от 27.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №3937</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2722,39 +2717,39 @@
         </is>
       </c>
       <c r="C63" s="2" t="n">
-        <v>119150000</v>
+        <v>47896000</v>
       </c>
       <c r="D63" s="2" t="n"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Angren Sut Mahsulotlari MChJ</t>
+          <t>Mehnat Agro Servis AJ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>280529819</t>
+          <t>252981962</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000231471188001</t>
+          <t>20208000147118816001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №2240</t>
+          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО С/Ф №3579</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>29.07.2026</t>
+          <t>04.08.2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2764,38 +2759,38 @@
       </c>
       <c r="C64" s="2" t="n"/>
       <c r="D64" s="2" t="n">
-        <v>21457000</v>
+        <v>11525000</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Omad Un Mahsulotlari MChJ</t>
+          <t>Kamalak Logistik MChJ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>216111455</t>
+          <t>311145569</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20208000988148375001</t>
+          <t>20208000814837533001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №171/26, НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №2266 от 04.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>29.07.2026</t>
+          <t>05.08.2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2803,40 +2798,40 @@
           <t>155</t>
         </is>
       </c>
-      <c r="C65" s="2" t="n">
-        <v>12487000</v>
-      </c>
-      <c r="D65" s="2" t="n"/>
+      <c r="C65" s="2" t="n"/>
+      <c r="D65" s="2" t="n">
+        <v>29090000</v>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Angren Sut Mahsulotlari MChJ</t>
+          <t>Kamalak Logistik MChJ</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>280529819</t>
+          <t>311145569</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20208000231471188001</t>
+          <t>20208000814837533001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>MATERIALLAR UCHUN OLDINDAN TO'LOV, SHARTNOMA №289/26</t>
+          <t>Оплата по счет-фактуре №7946 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>30.07.2026</t>
+          <t>05.08.2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2845,39 +2840,34 @@
         </is>
       </c>
       <c r="C66" s="2" t="n">
-        <v>24255000</v>
+        <v>101251000</v>
       </c>
       <c r="D66" s="2" t="n"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Angren Sut Mahsulotlari MChJ</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>280529819</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000231471188001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №8/26, QQS bilan</t>
+          <t>Заработная плата за июль 2026 г. (перечисление на пластиковые карты)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>05.08.2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2885,40 +2875,35 @@
           <t>157</t>
         </is>
       </c>
-      <c r="C67" s="2" t="n"/>
-      <c r="D67" s="2" t="n">
-        <v>27322000</v>
-      </c>
+      <c r="C67" s="2" t="n">
+        <v>109900000</v>
+      </c>
+      <c r="D67" s="2" t="n"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Omad Un Mahsulotlari MChJ</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>216111455</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-9972)</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000988148375001</t>
+          <t>16307000394306942417</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №7353 за поставленный товар</t>
+          <t>Kredit shartnomasi L-2024-9972 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>06.08.2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2928,38 +2913,38 @@
       </c>
       <c r="C68" s="2" t="n"/>
       <c r="D68" s="2" t="n">
-        <v>21694000</v>
+        <v>272152000</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Jizzax Tikuv XK</t>
+          <t>Lazzat Mato MChJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>234951170</t>
+          <t>219159581</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000692708815001</t>
+          <t>20208000380906903001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №6/26, НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №6878 от 06.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>06.08.2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2969,38 +2954,38 @@
       </c>
       <c r="C69" s="2" t="n"/>
       <c r="D69" s="2" t="n">
-        <v>21622000</v>
+        <v>21384000</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Omad Un Mahsulotlari MChJ</t>
+          <t>Lazzat Mato MChJ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>216111455</t>
+          <t>219159581</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000988148375001</t>
+          <t>20208000380906903001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №180/26, НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №1062 от 06.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>06.08.2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3008,40 +2993,40 @@
           <t>160</t>
         </is>
       </c>
-      <c r="C70" s="2" t="n"/>
-      <c r="D70" s="2" t="n">
-        <v>16866000</v>
-      </c>
+      <c r="C70" s="2" t="n">
+        <v>9166000</v>
+      </c>
+      <c r="D70" s="2" t="n"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Omad Un Mahsulotlari MChJ</t>
+          <t>Termiz Qurilish MChJ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>216111455</t>
+          <t>394974967</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000988148375001</t>
+          <t>20208000335850400001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №155/26 от 31.07.2026</t>
+          <t>Оплата за товары согласно с/ф №3220</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3050,34 +3035,39 @@
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>300000</v>
+        <v>21643000</v>
       </c>
       <c r="D71" s="2" t="n"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Termiz Qurilish MChJ</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>394974967</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000335850400001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Bank xizmati uchun komissiya</t>
+          <t>Оплата за товары согласно счет-фактуре №4308</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3085,23 +3075,23 @@
           <t>162</t>
         </is>
       </c>
-      <c r="C72" s="2" t="n"/>
-      <c r="D72" s="2" t="n">
-        <v>21966000</v>
-      </c>
+      <c r="C72" s="2" t="n">
+        <v>45999000</v>
+      </c>
+      <c r="D72" s="2" t="n"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Oqtosh Qurilish MChJ</t>
+          <t>Termiz Qurilish MChJ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>234191595</t>
+          <t>394974967</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000183809069001</t>
+          <t>20208000335850400001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3111,14 +3101,14 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №311 от 03.08.2026, в т.ч. НДС 12%</t>
+          <t>Tovarlar uchun o'lov h/f №7306</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3128,38 +3118,38 @@
       </c>
       <c r="C73" s="2" t="n"/>
       <c r="D73" s="2" t="n">
-        <v>14785000</v>
+        <v>42343000</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Omad Un Mahsulotlari MChJ</t>
+          <t>Jizzax Logistik MChJ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>216111455</t>
+          <t>295117016</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000988148375001</t>
+          <t>20208000270881567001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №7432 от 03.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата по счет-фактуре №3781 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3167,40 +3157,40 @@
           <t>164</t>
         </is>
       </c>
-      <c r="C74" s="2" t="n">
-        <v>77397000</v>
-      </c>
-      <c r="D74" s="2" t="n"/>
+      <c r="C74" s="2" t="n"/>
+      <c r="D74" s="2" t="n">
+        <v>11738000</v>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Angren Sut Mahsulotlari MChJ</t>
+          <t>Kamalak Logistik MChJ</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>280529819</t>
+          <t>311145569</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20208000231471188001</t>
+          <t>20208000814837533001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №272/26, QQS bilan</t>
+          <t>Оплата за продукцию по договору №84/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3209,39 +3199,39 @@
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>142893000</v>
+        <v>13791000</v>
       </c>
       <c r="D75" s="2" t="n"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ilhom Avto Ehtiyot MChJ</t>
+          <t>Urganch Qurilish Materiallari AJ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>240223444</t>
+          <t>257886564</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20208000946555911001</t>
+          <t>20208000155605963001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по дог. №90/26</t>
+          <t>Аренда помещения за август, дог. №72/21</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>04.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3249,40 +3239,40 @@
           <t>166</t>
         </is>
       </c>
-      <c r="C76" s="2" t="n"/>
-      <c r="D76" s="2" t="n">
-        <v>26296000</v>
-      </c>
+      <c r="C76" s="2" t="n">
+        <v>42007000</v>
+      </c>
+      <c r="D76" s="2" t="n"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Omad Un Mahsulotlari MChJ</t>
+          <t>Mehnat Agro Servis AJ</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>216111455</t>
+          <t>252981962</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>20208000988148375001</t>
+          <t>20208000147118816001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №265/26 от 04.08.2026</t>
+          <t>Xom ashyo uchun to'lov, shartn. №125/26, QQS blan</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>04.08.2026</t>
+          <t>11.08.2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3290,40 +3280,40 @@
           <t>167</t>
         </is>
       </c>
-      <c r="C77" s="2" t="n"/>
-      <c r="D77" s="2" t="n">
-        <v>16060000</v>
-      </c>
+      <c r="C77" s="2" t="n">
+        <v>17246000</v>
+      </c>
+      <c r="D77" s="2" t="n"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Chirchiq Meva Eksport XK</t>
+          <t>Termiz Qurilish MChJ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>259949749</t>
+          <t>394974967</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>20208000783358504001</t>
+          <t>20208000335850400001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №9805 от 04.08.2026, в т.ч. НДС 12%</t>
+          <t>Tovarlar uchun to'lov h/f №2410</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>04.08.2026</t>
+          <t>12.08.2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3331,35 +3321,40 @@
           <t>168</t>
         </is>
       </c>
-      <c r="C78" s="2" t="n">
-        <v>101251000</v>
-      </c>
-      <c r="D78" s="2" t="n"/>
+      <c r="C78" s="2" t="n"/>
+      <c r="D78" s="2" t="n">
+        <v>16339000</v>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Jizzax Logistik MChJ</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>295117016</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000270881567001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Заработная плата за июль 2026 г. (перечисление на пластиковые карты)</t>
+          <t>Оплата по счет-фактуре №7273 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>05.08.2026</t>
+          <t>13.08.2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3369,38 +3364,38 @@
       </c>
       <c r="C79" s="2" t="n"/>
       <c r="D79" s="2" t="n">
-        <v>33787000</v>
+        <v>27244000</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Namangan Sut MChJ</t>
+          <t>Lazzat Mato MChJ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>248247433</t>
+          <t>219159581</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000050167487001</t>
+          <t>20208000380906903001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №5336 за поставленный товар</t>
+          <t>Оплата по счет-фактуре №4066 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>05.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3408,40 +3403,40 @@
           <t>170</t>
         </is>
       </c>
-      <c r="C80" s="2" t="n"/>
-      <c r="D80" s="2" t="n">
-        <v>13969000</v>
-      </c>
+      <c r="C80" s="2" t="n">
+        <v>8346000</v>
+      </c>
+      <c r="D80" s="2" t="n"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Oqtosh Qurilish MChJ</t>
+          <t>Mehnat Agro Servis AJ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>234191595</t>
+          <t>252981962</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000183809069001</t>
+          <t>20208000147118816001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №1730 от 05.08.2026, в т.ч. НДС 12%</t>
+          <t>ОПЛАТА ЗА УПАКОВОЧНЫЕ МАТЕРИАЛЫ, С/Ф №3108</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>05.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3449,40 +3444,40 @@
           <t>171</t>
         </is>
       </c>
-      <c r="C81" s="2" t="n"/>
-      <c r="D81" s="2" t="n">
-        <v>12749000</v>
-      </c>
+      <c r="C81" s="2" t="n">
+        <v>13807000</v>
+      </c>
+      <c r="D81" s="2" t="n"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Yulduz Tikuv AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>263502137</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20208000123163885001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №48/26, НДС 12%</t>
+          <t>Социальный налог за июль 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>05.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3491,34 +3486,39 @@
         </is>
       </c>
       <c r="C82" s="2" t="n">
-        <v>109900000</v>
+        <v>13807000</v>
       </c>
       <c r="D82" s="2" t="n"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-9972)</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>16307000394306942417</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-9972 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>JShDS iyul oyi uchun</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>06.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3526,40 +3526,40 @@
           <t>173</t>
         </is>
       </c>
-      <c r="C83" s="2" t="n"/>
-      <c r="D83" s="2" t="n">
-        <v>14006000</v>
-      </c>
+      <c r="C83" s="2" t="n">
+        <v>71593000</v>
+      </c>
+      <c r="D83" s="2" t="n"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Omad Un Mahsulotlari MChJ</t>
+          <t>Afrosiyob Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>216111455</t>
+          <t>354981983</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000988148375001</t>
+          <t>20208000002477817001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №2666 за поставленный товар</t>
+          <t>Оплата за сырье по договору №69/26 от 17.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>06.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3567,40 +3567,40 @@
           <t>174</t>
         </is>
       </c>
-      <c r="C84" s="2" t="n"/>
-      <c r="D84" s="2" t="n">
-        <v>13079000</v>
-      </c>
+      <c r="C84" s="2" t="n">
+        <v>1087534000</v>
+      </c>
+      <c r="D84" s="2" t="n"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Omad Un Mahsulotlari MChJ</t>
+          <t>Mehnat Agro Servis AJ</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>216111455</t>
+          <t>252981962</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>20208000988148375001</t>
+          <t>20208000147118816001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №8/26, НДС 12%</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №58/26</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>18.08.2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3610,21 +3610,21 @@
       </c>
       <c r="C85" s="2" t="n"/>
       <c r="D85" s="2" t="n">
-        <v>296998000</v>
+        <v>62884000</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Oqtosh Qurilish MChJ</t>
+          <t>Urganch Agro Servis AJ</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>234191595</t>
+          <t>287747109</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000183809069001</t>
+          <t>20208000165940307001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -3634,14 +3634,14 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №17/26 от 07.08.2026</t>
+          <t>Оплата по счет-фактуре №2638 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3651,38 +3651,38 @@
       </c>
       <c r="C86" s="2" t="n"/>
       <c r="D86" s="2" t="n">
-        <v>89685000</v>
+        <v>25390000</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Omad Un Mahsulotlari MChJ</t>
+          <t>Kamalak Logistik MChJ</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>216111455</t>
+          <t>311145569</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000988148375001</t>
+          <t>20208000814837533001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №245/26, QQS 12%</t>
+          <t>Оплата по счет-фактуре №7132 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3692,38 +3692,38 @@
       </c>
       <c r="C87" s="2" t="n"/>
       <c r="D87" s="2" t="n">
-        <v>150167000</v>
+        <v>11915000</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Omad Un Mahsulotlari MChJ</t>
+          <t>Lazzat Mato MChJ</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>216111455</t>
+          <t>219159581</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000988148375001</t>
+          <t>20208000380906903001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №1252 от 10.08.2026, в т.ч. НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №2367 21.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3731,40 +3731,40 @@
           <t>178</t>
         </is>
       </c>
-      <c r="C88" s="2" t="n"/>
-      <c r="D88" s="2" t="n">
-        <v>26287000</v>
-      </c>
+      <c r="C88" s="2" t="n">
+        <v>8619000</v>
+      </c>
+      <c r="D88" s="2" t="n"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Andijon Qurilish Materiallari MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>259709555</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000755707627001</t>
+          <t>20208000501793101001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3580</t>
+          <t>Оплата за электроэнергию согласно счету</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3773,39 +3773,39 @@
         </is>
       </c>
       <c r="C89" s="2" t="n">
-        <v>13791000</v>
+        <v>17872000</v>
       </c>
       <c r="D89" s="2" t="n"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Buxoro Qurilish MChJ</t>
+          <t>Mehnat Agro Servis AJ</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>275672982</t>
+          <t>252981962</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20208000548740249001</t>
+          <t>20208000147118816001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>BINO IJARASI UCHUN TO'LOV AVGUST</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №45/26</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3814,39 +3814,39 @@
         </is>
       </c>
       <c r="C90" s="2" t="n">
-        <v>55276000</v>
+        <v>22737000</v>
       </c>
       <c r="D90" s="2" t="n"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Ilhom Avto Ehtiyot MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>240223444</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000946555911001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №9920</t>
+          <t>Уплата налога на добавленную стоимость за июль</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3854,40 +3854,40 @@
           <t>181</t>
         </is>
       </c>
-      <c r="C91" s="2" t="n">
-        <v>165535000</v>
-      </c>
-      <c r="D91" s="2" t="n"/>
+      <c r="C91" s="2" t="n"/>
+      <c r="D91" s="2" t="n">
+        <v>62366000</v>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Qarshi Yog'och XK</t>
+          <t>Kamalak Logistik MChJ</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>335788656</t>
+          <t>311145569</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000915560596001</t>
+          <t>20208000814837533001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №54/26 от 10.08.2026, НДС 12%</t>
+          <t>Оплата по счет-фактуре №8458 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3896,39 +3896,39 @@
         </is>
       </c>
       <c r="C92" s="2" t="n">
-        <v>349741000</v>
+        <v>6511000</v>
       </c>
       <c r="D92" s="2" t="n"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Angren Sut Mahsulotlari MChJ</t>
+          <t>Termiz Qurilish MChJ</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>280529819</t>
+          <t>394974967</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000231471188001</t>
+          <t>20208000335850400001</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №9807</t>
+          <t>Оплата за упаковочные материалы, с/ф №2381</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>11.08.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3936,40 +3936,40 @@
           <t>183</t>
         </is>
       </c>
-      <c r="C93" s="2" t="n"/>
-      <c r="D93" s="2" t="n">
-        <v>15447000</v>
-      </c>
+      <c r="C93" s="2" t="n">
+        <v>53303000</v>
+      </c>
+      <c r="D93" s="2" t="n"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Omad Un Mahsulotlari MChJ</t>
+          <t>Termiz Qurilish MChJ</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>216111455</t>
+          <t>394974967</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20208000988148375001</t>
+          <t>20208000335850400001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №100/26 от 11.08.2026</t>
+          <t>Tovarlar uchun to'lov h/f №497</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>12.08.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3978,39 +3978,39 @@
         </is>
       </c>
       <c r="C94" s="2" t="n">
-        <v>63790000</v>
+        <v>87230000</v>
       </c>
       <c r="D94" s="2" t="n"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Angren Sut Mahsulotlari MChJ</t>
+          <t>Afrosiyob Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>280529819</t>
+          <t>354981983</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000231471188001</t>
+          <t>20208000002477817001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №4/26</t>
+          <t>Оплата за упаковочные материалы с/ф №4102</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>13.08.2026</t>
+          <t>26.08.2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4020,38 +4020,38 @@
       </c>
       <c r="C95" s="2" t="n"/>
       <c r="D95" s="2" t="n">
-        <v>14122000</v>
+        <v>16432000</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Omad Un Mahsulotlari MChJ</t>
+          <t>Kamalak Logistik MChJ</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>216111455</t>
+          <t>311145569</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000988148375001</t>
+          <t>20208000814837533001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №156/26 от 13.08.2026</t>
+          <t>Предоплата за товар по дог. №299/26 от 26.08.2026</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>14.08.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4061,21 +4061,21 @@
       </c>
       <c r="C96" s="2" t="n"/>
       <c r="D96" s="2" t="n">
-        <v>18787000</v>
+        <v>52136000</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Oqtosh Qurilish MChJ</t>
+          <t>Jizzax Logistik MChJ</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>234191595</t>
+          <t>295117016</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>20208000183809069001</t>
+          <t>20208000270881567001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4085,14 +4085,14 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №6/26, НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №177/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4100,40 +4100,40 @@
           <t>187</t>
         </is>
       </c>
-      <c r="C97" s="2" t="n"/>
-      <c r="D97" s="2" t="n">
-        <v>90847000</v>
-      </c>
+      <c r="C97" s="2" t="n">
+        <v>8774000</v>
+      </c>
+      <c r="D97" s="2" t="n"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Omad Un Mahsulotlari MChJ</t>
+          <t>Afrosiyob Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>216111455</t>
+          <t>354981983</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>20208000988148375001</t>
+          <t>20208000002477817001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №5747 от 17.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товары согласно счет-фактуре №1882</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>28.08.2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4143,21 +4143,21 @@
       </c>
       <c r="C98" s="2" t="n"/>
       <c r="D98" s="2" t="n">
-        <v>34893000</v>
+        <v>13317000</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Oqtosh Qurilish MChJ</t>
+          <t>Kamalak Logistik MChJ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>234191595</t>
+          <t>311145569</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000183809069001</t>
+          <t>20208000814837533001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4167,14 +4167,14 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Shartnoma №278/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за товар по договору №77/26 от 28.08.2026</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>28.08.2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4182,40 +4182,40 @@
           <t>189</t>
         </is>
       </c>
-      <c r="C99" s="2" t="n"/>
-      <c r="D99" s="2" t="n">
-        <v>14191000</v>
-      </c>
+      <c r="C99" s="2" t="n">
+        <v>39707000</v>
+      </c>
+      <c r="D99" s="2" t="n"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Chirchiq Meva Eksport XK</t>
+          <t>Termiz Qurilish MChJ</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>259949749</t>
+          <t>394974967</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000783358504001</t>
+          <t>20208000335850400001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №16/26, НДС 12%</t>
+          <t>Tovarlar uchun to'lo h/f №6871</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4223,40 +4223,40 @@
           <t>190</t>
         </is>
       </c>
-      <c r="C100" s="2" t="n">
-        <v>13807000</v>
-      </c>
-      <c r="D100" s="2" t="n"/>
+      <c r="C100" s="2" t="n"/>
+      <c r="D100" s="2" t="n">
+        <v>141289000</v>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Kamalak Logistik MChJ</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>311145569</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000814837533001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Социальный налог за июль 2026 г.</t>
+          <t>Tovar uchun to'lov, hisob-faktura №3949 31.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4265,39 +4265,34 @@
         </is>
       </c>
       <c r="C101" s="2" t="n">
-        <v>13807000</v>
+        <v>300000</v>
       </c>
       <c r="D101" s="2" t="n"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>201122905</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Jismoniy shaxslar daromad solig'i iyul 2026</t>
+          <t>Bank xizmati uchun komissiya</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4306,39 +4301,39 @@
         </is>
       </c>
       <c r="C102" s="2" t="n">
-        <v>107314000</v>
+        <v>7583000</v>
       </c>
       <c r="D102" s="2" t="n"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Angren Sut Mahsulotlari MChJ</t>
+          <t>Nurafshon Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>280529819</t>
+          <t>370955507</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000231471188001</t>
+          <t>20208000570762728001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №123/26</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №182/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4347,39 +4342,39 @@
         </is>
       </c>
       <c r="C103" s="2" t="n">
-        <v>337421000</v>
+        <v>17879000</v>
       </c>
       <c r="D103" s="2" t="n"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Angren Sut Mahsulotlari MChJ</t>
+          <t>Termiz Qurilish MChJ</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>280529819</t>
+          <t>394974967</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>20208000231471188001</t>
+          <t>20208000335850400001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №7038</t>
+          <t>ОПЛАТА ЗА УПАКОВОЧНЫЕ МАТЕРИАЛЫ, С/Ф №7419</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>20.08.2026</t>
+          <t>01.09.2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4387,23 +4382,23 @@
           <t>194</t>
         </is>
       </c>
-      <c r="C104" s="2" t="n"/>
-      <c r="D104" s="2" t="n">
-        <v>20251000</v>
-      </c>
+      <c r="C104" s="2" t="n">
+        <v>42007000</v>
+      </c>
+      <c r="D104" s="2" t="n"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Oqtosh Qurilish MChJ</t>
+          <t>Termiz Qurilish MChJ</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>234191595</t>
+          <t>394974967</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000183809069001</t>
+          <t>20208000335850400001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -4413,14 +4408,14 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №91/26, НДС 12%</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №232/26</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>20.08.2026</t>
+          <t>02.09.2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4430,21 +4425,21 @@
       </c>
       <c r="C105" s="2" t="n"/>
       <c r="D105" s="2" t="n">
-        <v>18081000</v>
+        <v>112428000</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Oqtosh Qurilish MChJ</t>
+          <t>Jizzax Logistik MChJ</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>234191595</t>
+          <t>295117016</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000183809069001</t>
+          <t>20208000270881567001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -4454,14 +4449,14 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №1263 от 20.08.2026, в т.ч. НДС 12%</t>
+          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №8358</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>02.09.2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4469,40 +4464,40 @@
           <t>196</t>
         </is>
       </c>
-      <c r="C106" s="2" t="n"/>
-      <c r="D106" s="2" t="n">
-        <v>32474000</v>
-      </c>
+      <c r="C106" s="2" t="n">
+        <v>50900000</v>
+      </c>
+      <c r="D106" s="2" t="n"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Omad Un Mahsulotlari MChJ</t>
+          <t>Termiz Qurilish MChJ</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>216111455</t>
+          <t>394974967</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20208000988148375001</t>
+          <t>20208000335850400001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Shartnoma №160/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за материалы по договору №56/26</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4510,40 +4505,40 @@
           <t>197</t>
         </is>
       </c>
-      <c r="C107" s="2" t="n">
-        <v>23297000</v>
-      </c>
-      <c r="D107" s="2" t="n"/>
+      <c r="C107" s="2" t="n"/>
+      <c r="D107" s="2" t="n">
+        <v>154928000</v>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Samarqand Savdo MChJ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>324743320</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000016748722001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>УПЛАТА НАЛОГА НА ДОБАВЛЕННУЮ СТОИМОСТЬ ЗА ИЮЛЬ</t>
+          <t>Оплата за продукцию по дог. №217/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4551,40 +4546,35 @@
           <t>198</t>
         </is>
       </c>
-      <c r="C108" s="2" t="n"/>
-      <c r="D108" s="2" t="n">
-        <v>89913000</v>
-      </c>
+      <c r="C108" s="2" t="n">
+        <v>97419000</v>
+      </c>
+      <c r="D108" s="2" t="n"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Yulduz Tikuv AJ</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>263502137</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000123163885001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №7631 за поставленный товар</t>
+          <t>Ish haqi to'lovi avgust 2026 (plastik kartalarga)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>05.09.2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4592,40 +4582,35 @@
           <t>199</t>
         </is>
       </c>
-      <c r="C109" s="2" t="n"/>
-      <c r="D109" s="2" t="n">
-        <v>35225000</v>
-      </c>
+      <c r="C109" s="2" t="n">
+        <v>109900000</v>
+      </c>
+      <c r="D109" s="2" t="n"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Omad Un Mahsulotlari MChJ</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>216111455</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-9972)</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000988148375001</t>
+          <t>16307000394306942417</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Shartnoma №229/26 bo'yicha oldindan to'lov</t>
+          <t>Kredit shartnomasi L-2024-9972 bo'yicha navbatdagi to'lov (09.2026)</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4635,38 +4620,38 @@
       </c>
       <c r="C110" s="2" t="n"/>
       <c r="D110" s="2" t="n">
-        <v>34846000</v>
+        <v>154958000</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Namangan Sut MChJ</t>
+          <t>Kamalak Logistik MChJ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>248247433</t>
+          <t>311145569</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000050167487001</t>
+          <t>20208000814837533001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №6054 за поставленный товар</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №4836</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>08.09.2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4674,40 +4659,40 @@
           <t>201</t>
         </is>
       </c>
-      <c r="C111" s="2" t="n"/>
-      <c r="D111" s="2" t="n">
-        <v>28930000</v>
-      </c>
+      <c r="C111" s="2" t="n">
+        <v>13269000</v>
+      </c>
+      <c r="D111" s="2" t="n"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Omad Un Mahsulotlari MChJ</t>
+          <t>Urganch Qurilish Materiallari AJ</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>216111455</t>
+          <t>257886564</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000988148375001</t>
+          <t>20208000155605963001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2946 от 24.08.2026, в т.ч. НДС 12%</t>
+          <t>Аренда помещения за сентябрь, дог. №72/21</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>09.09.2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4717,38 +4702,38 @@
       </c>
       <c r="C112" s="2" t="n"/>
       <c r="D112" s="2" t="n">
-        <v>21782000</v>
+        <v>57619000</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Omad Un Mahsulotlari MChJ</t>
+          <t>Kamalak Logistik MChJ</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>216111455</t>
+          <t>311145569</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>20208000988148375001</t>
+          <t>20208000814837533001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9203 от 24.08.2026, в т.ч. НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №6412 09.09.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>09.09.2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4756,40 +4741,40 @@
           <t>203</t>
         </is>
       </c>
-      <c r="C113" s="2" t="n">
-        <v>8619000</v>
-      </c>
-      <c r="D113" s="2" t="n"/>
+      <c r="C113" s="2" t="n"/>
+      <c r="D113" s="2" t="n">
+        <v>42743000</v>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Kamalak Logistik MChJ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>311145569</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000489915123001</t>
+          <t>20208000814837533001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию согласно счету</t>
+          <t>Оплата по счет-фактуре №4263 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>09.09.2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4797,40 +4782,40 @@
           <t>204</t>
         </is>
       </c>
-      <c r="C114" s="2" t="n">
-        <v>62857000</v>
-      </c>
-      <c r="D114" s="2" t="n"/>
+      <c r="C114" s="2" t="n"/>
+      <c r="D114" s="2" t="n">
+        <v>26783000</v>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Ilhom Avto Ehtiyot MChJ</t>
+          <t>Lazzat Mato MChJ</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>240223444</t>
+          <t>219159581</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000946555911001</t>
+          <t>20208000380906903001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>XOM ASHYO UCHUN TO'LOV, SHARTNOMA №188/26, QQS BILAN</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5956</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>09.09.2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4839,39 +4824,39 @@
         </is>
       </c>
       <c r="C115" s="2" t="n">
-        <v>109096000</v>
+        <v>49038000</v>
       </c>
       <c r="D115" s="2" t="n"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Sharq Un Mahsulotlari XK</t>
+          <t>Termiz Qurilish MChJ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>227213724</t>
+          <t>394974967</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20208000657957353001</t>
+          <t>20208000335850400001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №110/26</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №88/26</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
+          <t>10.09.2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4879,40 +4864,40 @@
           <t>206</t>
         </is>
       </c>
-      <c r="C116" s="2" t="n">
-        <v>63595000</v>
-      </c>
-      <c r="D116" s="2" t="n"/>
+      <c r="C116" s="2" t="n"/>
+      <c r="D116" s="2" t="n">
+        <v>121185000</v>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Angren Sut Mahsulotlari MChJ</t>
+          <t>Kamalak Logistik MChJ</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>280529819</t>
+          <t>311145569</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000231471188001</t>
+          <t>20208000814837533001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №3130</t>
+          <t>Оплата по счет-фактуре №1499 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4922,38 +4907,38 @@
       </c>
       <c r="C117" s="2" t="n"/>
       <c r="D117" s="2" t="n">
-        <v>136559000</v>
+        <v>120944000</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Omad Un Mahsulotlari MChJ</t>
+          <t>Lazzat Mato MChJ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>216111455</t>
+          <t>219159581</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000988148375001</t>
+          <t>20208000380906903001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №5861 за поставленный товар</t>
+          <t>Оплата за продукцию по договору №137/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4961,40 +4946,40 @@
           <t>208</t>
         </is>
       </c>
-      <c r="C118" s="2" t="n"/>
-      <c r="D118" s="2" t="n">
-        <v>85311000</v>
-      </c>
+      <c r="C118" s="2" t="n">
+        <v>28796000</v>
+      </c>
+      <c r="D118" s="2" t="n"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Durdona Oziq-ovqat Savdo XK</t>
+          <t>Nurafshon Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>280877471</t>
+          <t>370955507</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000981659403001</t>
+          <t>20208000570762728001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №83/26, НДС 12%</t>
+          <t>Оплата за транспортные услуги по договору №77/26</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5002,40 +4987,40 @@
           <t>209</t>
         </is>
       </c>
-      <c r="C119" s="2" t="n"/>
-      <c r="D119" s="2" t="n">
-        <v>36636000</v>
-      </c>
+      <c r="C119" s="2" t="n">
+        <v>54871000</v>
+      </c>
+      <c r="D119" s="2" t="n"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Omad Un Mahsulotlari MChJ</t>
+          <t>Termiz Qurilish MChJ</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>216111455</t>
+          <t>394974967</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000988148375001</t>
+          <t>20208000335850400001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №239/26 ОТ 27.08.2026</t>
+          <t>Предоплата за материалы по договору №56/26</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5043,40 +5028,40 @@
           <t>210</t>
         </is>
       </c>
-      <c r="C120" s="2" t="n"/>
-      <c r="D120" s="2" t="n">
-        <v>12520000</v>
-      </c>
+      <c r="C120" s="2" t="n">
+        <v>193775000</v>
+      </c>
+      <c r="D120" s="2" t="n"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Omad Un Mahsulotlari MChJ</t>
+          <t>Afrosiyob Qurilish XK</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>216111455</t>
+          <t>291470952</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000988148375001</t>
+          <t>20208000323657736001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7680</t>
+          <t>Оплата за транспортные услуги по договору №59/26</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>28.08.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5084,40 +5069,40 @@
           <t>211</t>
         </is>
       </c>
-      <c r="C121" s="2" t="n">
-        <v>22052000</v>
-      </c>
-      <c r="D121" s="2" t="n"/>
+      <c r="C121" s="2" t="n"/>
+      <c r="D121" s="2" t="n">
+        <v>77408000</v>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Sarbon Logistik MChJ</t>
+          <t>Kamalak Logistik MChJ</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>399038768</t>
+          <t>311145569</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>20208000109731235001</t>
+          <t>20208000814837533001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №120/26</t>
+          <t>Предоплата за товар по договору №285/26 от 15.09.2026</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5125,40 +5110,40 @@
           <t>212</t>
         </is>
       </c>
-      <c r="C122" s="2" t="n"/>
-      <c r="D122" s="2" t="n">
-        <v>227684000</v>
-      </c>
+      <c r="C122" s="2" t="n">
+        <v>13284000</v>
+      </c>
+      <c r="D122" s="2" t="n"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Omad Un Mahsulotlari MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>216111455</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000988148375001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №162/26, НДС 12%</t>
+          <t>Социальный налог за август 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5166,40 +5151,40 @@
           <t>213</t>
         </is>
       </c>
-      <c r="C123" s="2" t="n"/>
-      <c r="D123" s="2" t="n">
-        <v>139115000</v>
-      </c>
+      <c r="C123" s="2" t="n">
+        <v>13284000</v>
+      </c>
+      <c r="D123" s="2" t="n"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Omad Un Mahsulotlari MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>216111455</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000988148375001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №7286 за поставленный товар</t>
+          <t>Налог на доходы физических лиц за август 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5207,40 +5192,40 @@
           <t>214</t>
         </is>
       </c>
-      <c r="C124" s="2" t="n"/>
-      <c r="D124" s="2" t="n">
-        <v>64664000</v>
-      </c>
+      <c r="C124" s="2" t="n">
+        <v>191686000</v>
+      </c>
+      <c r="D124" s="2" t="n"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Omad Un Mahsulotlari MChJ</t>
+          <t>Mehnat Agro Servis AJ</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>216111455</t>
+          <t>252981962</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>20208000988148375001</t>
+          <t>20208000147118816001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №272/26, НДС 12%</t>
+          <t>Оплата за транспортные услуги по договору №141/26</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5250,21 +5235,21 @@
       </c>
       <c r="C125" s="2" t="n"/>
       <c r="D125" s="2" t="n">
-        <v>39289000</v>
+        <v>87827000</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Oqtosh Qurilish MChJ</t>
+          <t>Kamalak Logistik MChJ</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>234191595</t>
+          <t>311145569</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20208000183809069001</t>
+          <t>20208000814837533001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -5274,14 +5259,14 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №7497 от 31.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за продукцию по договору №109/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>17.09.2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5289,35 +5274,40 @@
           <t>216</t>
         </is>
       </c>
-      <c r="C126" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D126" s="2" t="n"/>
+      <c r="C126" s="2" t="n"/>
+      <c r="D126" s="2" t="n">
+        <v>85460000</v>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Samarqand Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>324743320</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000016748722001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>КОМИССИЯ ЗА ПЕРЕВОД</t>
+          <t>Tovar uchun to'lov, hisob-faktura №8215 17.09.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>17.09.2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5325,40 +5315,40 @@
           <t>217</t>
         </is>
       </c>
-      <c r="C127" s="2" t="n">
-        <v>24460000</v>
-      </c>
-      <c r="D127" s="2" t="n"/>
+      <c r="C127" s="2" t="n"/>
+      <c r="D127" s="2" t="n">
+        <v>35740000</v>
+      </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Angren Sut Mahsulotlari MChJ</t>
+          <t>Kamalak Logistik MChJ</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>280529819</t>
+          <t>311145569</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000231471188001</t>
+          <t>20208000814837533001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №187/26</t>
+          <t>Предоплата за товар по договору №12/26 от 17.09.2026</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5366,40 +5356,40 @@
           <t>218</t>
         </is>
       </c>
-      <c r="C128" s="2" t="n">
-        <v>74990000</v>
-      </c>
-      <c r="D128" s="2" t="n"/>
+      <c r="C128" s="2" t="n"/>
+      <c r="D128" s="2" t="n">
+        <v>43867000</v>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Qarshi Yog'och XK</t>
+          <t>Lazzat Mato MChJ</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>335788656</t>
+          <t>219159581</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>20208000915560596001</t>
+          <t>20208000380906903001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №8103</t>
+          <t>Оплата п счет-фактуре №1352 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>02.09.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5408,39 +5398,39 @@
         </is>
       </c>
       <c r="C129" s="2" t="n">
-        <v>113064000</v>
+        <v>45775000</v>
       </c>
       <c r="D129" s="2" t="n"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Ilhom Avto Ehtiyot MChJ</t>
+          <t>Termiz Qurilish MChJ</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>240223444</t>
+          <t>394974967</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>20208000946555911001</t>
+          <t>20208000335850400001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №91/26</t>
+          <t>Оплата за сырье по дог. №67/26 от 21.09.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>03.09.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5448,40 +5438,40 @@
           <t>220</t>
         </is>
       </c>
-      <c r="C130" s="2" t="n"/>
-      <c r="D130" s="2" t="n">
-        <v>24563000</v>
-      </c>
+      <c r="C130" s="2" t="n">
+        <v>81546000</v>
+      </c>
+      <c r="D130" s="2" t="n"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Omad Un Mahsulotlari MChJ</t>
+          <t>Mehnat Agro Servis AJ</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>216111455</t>
+          <t>252981962</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000988148375001</t>
+          <t>20208000147118816001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №64/26, НДС 12%</t>
+          <t>Оплата за сырье по договору№188/26 от 21.09.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>03.09.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5490,39 +5480,39 @@
         </is>
       </c>
       <c r="C131" s="2" t="n">
-        <v>35982000</v>
+        <v>344685000</v>
       </c>
       <c r="D131" s="2" t="n"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Xiva Polimer MChJ</t>
+          <t>Nurafshon Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>279310125</t>
+          <t>370955507</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000196619411001</t>
+          <t>20208000570762728001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №4/26</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №172/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>22.09.2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5530,40 +5520,40 @@
           <t>222</t>
         </is>
       </c>
-      <c r="C132" s="2" t="n"/>
-      <c r="D132" s="2" t="n">
-        <v>61081000</v>
-      </c>
+      <c r="C132" s="2" t="n">
+        <v>26653000</v>
+      </c>
+      <c r="D132" s="2" t="n"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Namangan Sut MChJ</t>
+          <t>Termiz Qurilish MChJ</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>248247433</t>
+          <t>394974967</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000050167487001</t>
+          <t>20208000335850400001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №9445 за поставленный товар</t>
+          <t>Оплата за транспортные услуги по договору №135/26</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>22.09.2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5571,40 +5561,40 @@
           <t>223</t>
         </is>
       </c>
-      <c r="C133" s="2" t="n"/>
-      <c r="D133" s="2" t="n">
-        <v>32151000</v>
-      </c>
+      <c r="C133" s="2" t="n">
+        <v>51411000</v>
+      </c>
+      <c r="D133" s="2" t="n"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Andijon Qurilish Materiallari MChJ</t>
+          <t>Nurafshon Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>259709555</t>
+          <t>370955507</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>20208000755707627001</t>
+          <t>20208000570762728001</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №209/26 от 04.09.2026</t>
+          <t>Оплата за товары согласно с/ф №9989</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>23.09.2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5612,35 +5602,40 @@
           <t>224</t>
         </is>
       </c>
-      <c r="C134" s="2" t="n">
-        <v>97419000</v>
-      </c>
-      <c r="D134" s="2" t="n"/>
+      <c r="C134" s="2" t="n"/>
+      <c r="D134" s="2" t="n">
+        <v>36608000</v>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Kamalak Logistik MChJ</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>311145569</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000814837533001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Заработная плата за август 2026 г. (перечисление на пластиковые карты)</t>
+          <t>Предоплата за товар по договору №210/26 от 23.09.2026</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>23.09.2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5649,39 +5644,39 @@
         </is>
       </c>
       <c r="C135" s="2" t="n">
-        <v>125353000</v>
+        <v>8293000</v>
       </c>
       <c r="D135" s="2" t="n"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Qarshi Yog'och XK</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>335788656</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>20208000915560596001</t>
+          <t>20208000501793101001</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №4908</t>
+          <t>Оплата за электроэнергию за сентябрь 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>05.09.2026</t>
+          <t>23.09.2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5690,34 +5685,39 @@
         </is>
       </c>
       <c r="C136" s="2" t="n">
-        <v>109900000</v>
+        <v>22351000</v>
       </c>
       <c r="D136" s="2" t="n"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-9972)</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>16307000394306942417</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-9972 bo'yicha navbatdagi to'lov (09.2026)</t>
+          <t>Уплата налога на добавленную стоимость за август</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>23.09.2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5725,23 +5725,23 @@
           <t>227</t>
         </is>
       </c>
-      <c r="C137" s="2" t="n"/>
-      <c r="D137" s="2" t="n">
-        <v>124439000</v>
-      </c>
+      <c r="C137" s="2" t="n">
+        <v>38915000</v>
+      </c>
+      <c r="D137" s="2" t="n"/>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Oqtosh Qurilish MChJ</t>
+          <t>Termiz Qurilish MChJ</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>234191595</t>
+          <t>394974967</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>20208000183809069001</t>
+          <t>20208000335850400001</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -5751,14 +5751,14 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №4378 от 07.09.2026, в т.ч. НДС 12%</t>
+          <t>Xom ashyo uchun to'lov, shartn. №216/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>25.09.2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5768,38 +5768,38 @@
       </c>
       <c r="C138" s="2" t="n"/>
       <c r="D138" s="2" t="n">
-        <v>25864000</v>
+        <v>155942000</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Omad Un Mahsulotlari MChJ</t>
+          <t>Kamalak Logistik MChJ</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>216111455</t>
+          <t>311145569</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>20208000988148375001</t>
+          <t>20208000814837533001</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Shartnoma №181/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товар по счет-фактуре №8295 от 25.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>08.09.2026</t>
+          <t>25.09.2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5809,38 +5809,38 @@
       </c>
       <c r="C139" s="2" t="n"/>
       <c r="D139" s="2" t="n">
-        <v>204738000</v>
+        <v>141407000</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Andijon Qurilish Materiallari MChJ</t>
+          <t>Kattaqo'rg'on Logistik XK</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>259709555</t>
+          <t>250213761</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>20208000755707627001</t>
+          <t>20208000316388526001</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Shartnoma №158/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за товар по договору №59/26 от 25.09.2026</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>08.09.2026</t>
+          <t>25.09.2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5848,40 +5848,40 @@
           <t>230</t>
         </is>
       </c>
-      <c r="C140" s="2" t="n"/>
-      <c r="D140" s="2" t="n">
-        <v>44297000</v>
-      </c>
+      <c r="C140" s="2" t="n">
+        <v>32231000</v>
+      </c>
+      <c r="D140" s="2" t="n"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Jizzax Tikuv XK</t>
+          <t>Termiz Qurilish MChJ</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>234951170</t>
+          <t>394974967</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>20208000692708815001</t>
+          <t>20208000335850400001</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №3692 08.09.2026, QQS bilan</t>
+          <t>Оплата за сырье по договору №14/26 от 25.09.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>08.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5889,40 +5889,40 @@
           <t>231</t>
         </is>
       </c>
-      <c r="C141" s="2" t="n">
-        <v>13269000</v>
-      </c>
-      <c r="D141" s="2" t="n"/>
+      <c r="C141" s="2" t="n"/>
+      <c r="D141" s="2" t="n">
+        <v>157930000</v>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Buxoro Qurilish MChJ</t>
+          <t>Lazzat Mato MChJ</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>275672982</t>
+          <t>219159581</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>20208000548740249001</t>
+          <t>20208000380906903001</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Аренда помещения за сентябрь, дог. №28/25</t>
+          <t>Оплата по счет-фактуре №5378 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5932,38 +5932,38 @@
       </c>
       <c r="C142" s="2" t="n"/>
       <c r="D142" s="2" t="n">
-        <v>131759000</v>
+        <v>49857000</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Omad Un Mahsulotlari MChJ</t>
+          <t>Kamalak Logistik MChJ</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>216111455</t>
+          <t>311145569</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>20208000988148375001</t>
+          <t>20208000814837533001</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5034</t>
+          <t>Предоплата за товар по договору №263/26 от 28.09.2026</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5973,38 +5973,38 @@
       </c>
       <c r="C143" s="2" t="n"/>
       <c r="D143" s="2" t="n">
-        <v>27553000</v>
+        <v>46198000</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Namangan Sut MChJ</t>
+          <t>Kamalak Logistik MChJ</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>248247433</t>
+          <t>311145569</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>20208000050167487001</t>
+          <t>20208000814837533001</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №275/26 от 09.09.2026</t>
+          <t>Tovar uchun to'lov, hisob-faktura №6154 28.09.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>10.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6012,40 +6012,40 @@
           <t>234</t>
         </is>
       </c>
-      <c r="C144" s="2" t="n"/>
-      <c r="D144" s="2" t="n">
-        <v>55258000</v>
-      </c>
+      <c r="C144" s="2" t="n">
+        <v>38485000</v>
+      </c>
+      <c r="D144" s="2" t="n"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Omad Un Mahsulotlari MChJ</t>
+          <t>Mehnat Agro Servis AJ</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>216111455</t>
+          <t>252981962</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>20208000988148375001</t>
+          <t>20208000147118816001</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №259/26 ОТ 10.09.2026</t>
+          <t>Оплата за упаковочные материалы, с/ф №6412</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>11.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6053,40 +6053,40 @@
           <t>235</t>
         </is>
       </c>
-      <c r="C145" s="2" t="n"/>
-      <c r="D145" s="2" t="n">
-        <v>114241000</v>
-      </c>
+      <c r="C145" s="2" t="n">
+        <v>41864000</v>
+      </c>
+      <c r="D145" s="2" t="n"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Omad Un Mahsulotlari MChJ</t>
+          <t>Afrosiyob Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>216111455</t>
+          <t>354981983</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>20208000988148375001</t>
+          <t>20208000002477817001</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6543</t>
+          <t>Оплата за товары согласно счет-фактуре №170</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>11.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -6095,39 +6095,39 @@
         </is>
       </c>
       <c r="C146" s="2" t="n">
-        <v>74324000</v>
+        <v>50045000</v>
       </c>
       <c r="D146" s="2" t="n"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Angren Sut Mahsulotlari MChJ</t>
+          <t>Termiz Qurilish MChJ</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>280529819</t>
+          <t>394974967</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>20208000231471188001</t>
+          <t>20208000335850400001</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №219/26 от 11.09.2026, НДС 12%</t>
+          <t>Оплата за транспортные услуги по дог. №27/26</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6135,40 +6135,40 @@
           <t>237</t>
         </is>
       </c>
-      <c r="C147" s="2" t="n"/>
-      <c r="D147" s="2" t="n">
-        <v>17604000</v>
-      </c>
+      <c r="C147" s="2" t="n">
+        <v>122268000</v>
+      </c>
+      <c r="D147" s="2" t="n"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Omad Un Mahsulotlari MChJ</t>
+          <t>Mehnat Agro Servis AJ</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>216111455</t>
+          <t>252981962</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>20208000988148375001</t>
+          <t>20208000147118816001</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №8617 от 14.09.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за материалы по договору №45/26</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>29.09.2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6176,40 +6176,40 @@
           <t>238</t>
         </is>
       </c>
-      <c r="C148" s="2" t="n">
-        <v>13284000</v>
-      </c>
-      <c r="D148" s="2" t="n"/>
+      <c r="C148" s="2" t="n"/>
+      <c r="D148" s="2" t="n">
+        <v>119345000</v>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Samarqand Savdo MChJ</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>324743320</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000016748722001</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Социальный налог за август 2026 г.</t>
+          <t>Предоплата за товар по договору №143/26 от 29.09.2026</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>29.09.2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6218,39 +6218,39 @@
         </is>
       </c>
       <c r="C149" s="2" t="n">
-        <v>13284000</v>
+        <v>91568000</v>
       </c>
       <c r="D149" s="2" t="n"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Termiz Qurilish MChJ</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>394974967</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000335850400001</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Налог на доходы физических лиц за август 2026 г.</t>
+          <t>Предоплата за материалы по дог. №239/26</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>30.09.2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -6258,23 +6258,23 @@
           <t>240</t>
         </is>
       </c>
-      <c r="C150" s="2" t="n">
-        <v>125611000</v>
-      </c>
-      <c r="D150" s="2" t="n"/>
+      <c r="C150" s="2" t="n"/>
+      <c r="D150" s="2" t="n">
+        <v>33437000</v>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Angren Sut Mahsulotlari MChJ</t>
+          <t>Lazzat Mato MChJ</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>280529819</t>
+          <t>219159581</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>20208000231471188001</t>
+          <t>20208000380906903001</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -6284,14 +6284,14 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №7772</t>
+          <t>Оплата по счет-фактуре №8068 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>30.09.2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6299,1366 +6299,54 @@
           <t>241</t>
         </is>
       </c>
-      <c r="C151" s="2" t="n"/>
-      <c r="D151" s="2" t="n">
-        <v>78142000</v>
-      </c>
+      <c r="C151" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D151" s="2" t="n"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Omad Un Mahsulotlari MChJ</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>216111455</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>20208000988148375001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №99/26, НДС 12%</t>
+          <t>КОМИССИЯ А ПЕРЕВОД</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>16.09.2026</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="n"/>
-      <c r="D152" s="2" t="n">
-        <v>126009000</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>Omad Un Mahsulotlari MChJ</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>216111455</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>20208000988148375001</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>Предоплата за товар по договору №5/26 от 16.09.2026</t>
-        </is>
+          <t>Jami aylanma:</t>
+        </is>
+      </c>
+      <c r="C152" s="4" t="n">
+        <v>5788526000</v>
+      </c>
+      <c r="D152" s="4" t="n">
+        <v>5738026000</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>16.09.2026</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="n"/>
-      <c r="D153" s="2" t="n">
-        <v>40608000</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>Omad Un Mahsulotlari MChJ</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>216111455</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>20208000988148375001</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>Предоплата за товар по дог. №172/26 от 16.09.2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>16.09.2026</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="n"/>
-      <c r="D154" s="2" t="n">
-        <v>27992000</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>Oqtosh Qurilish MChJ</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>234191595</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>20208000183809069001</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>Оплата за продукцию по договору №60/26, НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>18.09.2026</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="n"/>
-      <c r="D155" s="2" t="n">
-        <v>136252000</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>Omad Un Mahsulotlari MChJ</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>216111455</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>20208000988148375001</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>Оплата за продукцию по дог. №24/26, НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>18.09.2026</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="n"/>
-      <c r="D156" s="2" t="n">
-        <v>17921000</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>Durdona Oziq-ovqat Savdo XK</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>280877471</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>20208000981659403001</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №9157</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>21.09.2026</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>247</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="n"/>
-      <c r="D157" s="2" t="n">
-        <v>109003000</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>Omad Un Mahsulotlari MChJ</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>216111455</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>20208000988148375001</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>Shartnoma №126/26 bo'yicha oldindan to'lov</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>21.09.2026</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="n"/>
-      <c r="D158" s="2" t="n">
-        <v>45342000</v>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>Omad Un Mahsulotlari MChJ</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>216111455</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>20208000988148375001</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>Оплата за продукцию по договору №273/26, НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>21.09.2026</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>249</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="n"/>
-      <c r="D159" s="2" t="n">
-        <v>19086000</v>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>Omad Un Mahsulotlari MChJ</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>216111455</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>20208000988148375001</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>Оплата за товар по счет-фактуре №9920 от 21.09.2026, в т.ч. НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>21.09.2026</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="n"/>
-      <c r="D160" s="2" t="n">
-        <v>14426000</v>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>Oqtosh Qurilish MChJ</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>234191595</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>20208000183809069001</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>Оплата за товар по счет-фактуре №3862 от 21.09.2026, в т.ч. НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>21.09.2026</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="n">
-        <v>49239000</v>
-      </c>
-      <c r="D161" s="2" t="n"/>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>Angren Sut Mahsulotlari MChJ</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>280529819</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>20208000231471188001</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>Оплата за транспортные услуги по дог. №170/26</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>21.09.2026</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>252</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="n">
-        <v>67229000</v>
-      </c>
-      <c r="D162" s="2" t="n"/>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>Xiva Polimer MChJ</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>279310125</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>20208000196619411001</t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>Предоплата за материалы по дог. №64/26</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>22.09.2026</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="n">
-        <v>128449000</v>
-      </c>
-      <c r="D163" s="2" t="n"/>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>Angren Sut Mahsulotlari MChJ</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>280529819</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>20208000231471188001</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №89/26, QQS bilan</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>23.09.2026</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="n"/>
-      <c r="D164" s="2" t="n">
-        <v>31793000</v>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>Omad Un Mahsulotlari MChJ</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>216111455</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>20208000988148375001</t>
-        </is>
-      </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>Предоплата за товар по договору №259/26 от 23.09.2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>23.09.2026</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="n">
-        <v>8293000</v>
-      </c>
-      <c r="D165" s="2" t="n"/>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>200933985</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>20208000489915123001</t>
-        </is>
-      </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>Оплата за электроэнергию за сентябрь 2026 г.</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>23.09.2026</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="n">
-        <v>22336000</v>
-      </c>
-      <c r="D166" s="2" t="n"/>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>201122905</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>23402000300100001010</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>00014</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>УПЛАТА НАЛОГА НА ДОБАВЛЕННУЮ СТОИМОСТЬ ЗА АВГУСТ</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>23.09.2026</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="n">
-        <v>34100000</v>
-      </c>
-      <c r="D167" s="2" t="n"/>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>Angren Sut Mahsulotlari MChJ</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>280529819</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>20208000231471188001</t>
-        </is>
-      </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>Оплата за товары согласно счет-фактуре №615</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>23.09.2026</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="n">
-        <v>312513000</v>
-      </c>
-      <c r="D168" s="2" t="n"/>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>Sarbon Logistik MChJ</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>399038768</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>20208000109731235001</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>TRANSPORT XIZMATLARI UCHUN TO'LOV, SHARTNOMA №281/26</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>24.09.2026</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>259</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="n">
-        <v>117664000</v>
-      </c>
-      <c r="D169" s="2" t="n"/>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>Angren Sut Mahsulotlari MChJ</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>280529819</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>20208000231471188001</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>Оплата за товары согласно счет-фактуре №782</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>25.09.2026</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="n">
-        <v>23352000</v>
-      </c>
-      <c r="D170" s="2" t="n"/>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>Angren Sut Mahsulotlari MChJ</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>280529819</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>20208000231471188001</t>
-        </is>
-      </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>Оплата за упаковочные материалы, с/ф №9140</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>25.09.2026</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
-      </c>
-      <c r="C171" s="2" t="n">
-        <v>106179000</v>
-      </c>
-      <c r="D171" s="2" t="n"/>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>Ilhom Avto Ehtiyot MChJ</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>240223444</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>20208000946555911001</t>
-        </is>
-      </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>Оплата за упаковочные материалы, с/ф №6029</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="C172" s="2" t="n"/>
-      <c r="D172" s="2" t="n">
-        <v>105943000</v>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>Namangan Sut MChJ</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>248247433</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>20208000050167487001</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>Mahsulot uchun to'lov, shartnoma №87/26, QQS 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="C173" s="2" t="n"/>
-      <c r="D173" s="2" t="n">
-        <v>80519000</v>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>Omad Un Mahsulotlari MChJ</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>216111455</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>20208000988148375001</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>Оплата за продукцию по договору №33/26, НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="n"/>
-      <c r="D174" s="2" t="n">
-        <v>37800000</v>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>Oqtosh Qurilish MChJ</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>234191595</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>20208000183809069001</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>Shartnoma №198/26 bo'yicha oldindan to'lov</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="C175" s="2" t="n"/>
-      <c r="D175" s="2" t="n">
-        <v>20089000</v>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>Jizzax Tikuv XK</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>234951170</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>20208000692708815001</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>Оплата за товар по счет-фактуре №152 от 28.09.2026, в т.ч. НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>266</t>
-        </is>
-      </c>
-      <c r="C176" s="2" t="n"/>
-      <c r="D176" s="2" t="n">
-        <v>18428000</v>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>Oqtosh Qurilish MChJ</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>234191595</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>20208000183809069001</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>Shartnoma №123/26 bo'yicha oldindan to'lov</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>267</t>
-        </is>
-      </c>
-      <c r="C177" s="2" t="n">
-        <v>107949000</v>
-      </c>
-      <c r="D177" s="2" t="n"/>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>Qarshi Yog'och XK</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>335788656</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>20208000915560596001</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>Оплата за транспортные услуги по договору №288/26</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="C178" s="2" t="n">
-        <v>113193000</v>
-      </c>
-      <c r="D178" s="2" t="n"/>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>Sarbon Logistik MChJ</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>399038768</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>20208000109731235001</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>Оплата за сырье по договору №94/26 от 28.09.2026, НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>29.09.2026</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>269</t>
-        </is>
-      </c>
-      <c r="C179" s="2" t="n"/>
-      <c r="D179" s="2" t="n">
-        <v>34193000</v>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>Omad Un Mahsulotlari MChJ</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>216111455</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>20208000988148375001</t>
-        </is>
-      </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>Оплата за продукцию по договору №136/26, НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>29.09.2026</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="C180" s="2" t="n"/>
-      <c r="D180" s="2" t="n">
-        <v>30465000</v>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>Omad Un Mahsulotlari MChJ</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>216111455</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>20208000988148375001</t>
-        </is>
-      </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>Оплата за продукцию по договору №15/26, НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>29.09.2026</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="C181" s="2" t="n"/>
-      <c r="D181" s="2" t="n">
-        <v>23739000</v>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>Omad Un Mahsulotlari MChJ</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>216111455</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>20208000988148375001</t>
-        </is>
-      </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>Предоплата за товар по договору №39/26 от 29.09.2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>29.09.2026</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>272</t>
-        </is>
-      </c>
-      <c r="C182" s="2" t="n">
-        <v>57110000</v>
-      </c>
-      <c r="D182" s="2" t="n"/>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>Ilhom Avto Ehtiyot MChJ</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>240223444</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>20208000946555911001</t>
-        </is>
-      </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №77/26</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>30.09.2026</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
-      <c r="C183" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D183" s="2" t="n"/>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>Navbahor Bank ATB</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>45994000900000001001</t>
-        </is>
-      </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>Плата за SMS-информирование</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>Jami aylanma:</t>
-        </is>
-      </c>
-      <c r="C184" s="4" t="n">
-        <v>5835393000</v>
-      </c>
-      <c r="D184" s="4" t="n">
-        <v>5784893000</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
           <t>Davr oxiridagi qoldiq:</t>
         </is>
       </c>
-      <c r="C185" s="4" t="n">
+      <c r="C153" s="4" t="n">
         <v>642000000</v>
       </c>
-      <c r="D185" s="4" t="n"/>
+      <c r="D153" s="4" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
